--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/serie_temporal.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/serie_temporal.xlsx
@@ -89750,7 +89750,7 @@
         <v>71.63666666666667</v>
       </c>
       <c r="M2076" s="2" t="n">
-        <v>201.4259849088172</v>
+        <v>201.4259849088174</v>
       </c>
     </row>
     <row r="2077">
@@ -89793,7 +89793,7 @@
         <v>71.65333333333334</v>
       </c>
       <c r="M2077" s="2" t="n">
-        <v>201.539916519985</v>
+        <v>201.5399165199852</v>
       </c>
     </row>
   </sheetData>
@@ -89808,7 +89808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -90209,6 +90209,36 @@
         <v>0.5977</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde sup (px)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>2.0291</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde inf (px)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0.8895</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo peor / grosor (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1.009</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
